--- a/資料/全データ一覧_点検用.xlsx
+++ b/資料/全データ一覧_点検用.xlsx
@@ -22,7 +22,8 @@
     <sheet name="出来事" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="🔗 参照一覧" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="⚠ 参照エラー" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="⚠ 整合性チェック" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="📝 desc要編集" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="⚠ 整合性チェック" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'👤 人物'!$A$1:$K$15</definedName>
@@ -589,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出典: japan_history_data.json  version 19</t>
+          <t>出典: japan_history_data.json  version 20</t>
         </is>
       </c>
     </row>
@@ -3775,6 +3776,105 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>desc要編集（refs先の名前が元 desc に出てこないもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>検出件数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>※ 次回アップデートで「文中インラインリンク」に切り替える前に、ここが 0件 になるよう desc を編集してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>元 id</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>元 名前</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>元 カテゴリ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>元 desc 冒頭</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>先 id</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>先 名前</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>先 カテゴリ</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>推奨対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>全て desc 内に名前が含まれています — インラインリンク移行 OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
